--- a/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-predicted_mae.xlsx
+++ b/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-predicted_mae.xlsx
@@ -41,13 +41,13 @@
     <t xml:space="preserve">KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">Linear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Random Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAM</t>
   </si>
   <si>
     <t xml:space="preserve">Polynomial</t>
@@ -457,25 +457,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.131385409039121</v>
+        <v>0.139735680236785</v>
       </c>
       <c r="C3" t="n">
-        <v>0.122404513818609</v>
+        <v>0.111543457070267</v>
       </c>
       <c r="D3" t="n">
-        <v>0.17648924735296</v>
+        <v>0.183064642501266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.220867653910581</v>
+        <v>0.208065629542397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.109494059107694</v>
+        <v>0.120249523929429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.118693141133181</v>
+        <v>0.117528595418785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.146555670727024</v>
+        <v>0.146697921449821</v>
       </c>
     </row>
     <row r="4">
@@ -483,25 +483,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.139735680236785</v>
+        <v>0.142160584008359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.111543457070267</v>
+        <v>0.11332627837502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.183064642501266</v>
+        <v>0.191469763418863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.208065629542397</v>
+        <v>0.204985019152183</v>
       </c>
       <c r="F4" t="n">
-        <v>0.120249523929429</v>
+        <v>0.109623974294066</v>
       </c>
       <c r="G4" t="n">
-        <v>0.117528595418785</v>
+        <v>0.122699122950461</v>
       </c>
       <c r="H4" t="n">
-        <v>0.146697921449821</v>
+        <v>0.147377457033159</v>
       </c>
     </row>
     <row r="5">
@@ -509,25 +509,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.142160584008359</v>
+        <v>0.132768857269871</v>
       </c>
       <c r="C5" t="n">
-        <v>0.11332627837502</v>
+        <v>0.125260734698349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.191469763418863</v>
+        <v>0.176272141797044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.204985019152183</v>
+        <v>0.228945132374683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.109623974294066</v>
+        <v>0.105529371951593</v>
       </c>
       <c r="G5" t="n">
-        <v>0.122699122950461</v>
+        <v>0.116873431612429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.147377457033159</v>
+        <v>0.147608278283995</v>
       </c>
     </row>
     <row r="6">
